--- a/product_selector_out/STM32WL3x.xlsx
+++ b/product_selector_out/STM32WL3x.xlsx
@@ -1686,7 +1686,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6772,9 +6772,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7087,9 +7087,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7114,9 +7114,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -7429,9 +7429,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7798,9 +7798,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8113,9 +8113,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8140,9 +8140,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8455,9 +8455,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8482,9 +8482,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8797,9 +8797,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8824,9 +8824,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -9139,9 +9139,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9508,9 +9508,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9823,9 +9823,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9850,9 +9850,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10165,9 +10165,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10192,9 +10192,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10507,9 +10507,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10876,9 +10876,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11191,9 +11191,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WL3x.xlsx
+++ b/product_selector_out/STM32WL3x.xlsx
@@ -1686,7 +1686,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
         </is>
       </c>
     </row>
@@ -6772,9 +6772,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7087,9 +7087,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7114,9 +7114,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -7429,9 +7429,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7798,9 +7798,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8113,9 +8113,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8140,9 +8140,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8455,9 +8455,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8482,9 +8482,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8797,9 +8797,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8824,9 +8824,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -9139,9 +9139,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9508,9 +9508,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9823,9 +9823,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9850,9 +9850,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10165,9 +10165,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10192,9 +10192,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10507,9 +10507,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10876,9 +10876,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11191,9 +11191,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WL3x.xlsx
+++ b/product_selector_out/STM32WL3x.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9453125" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1005,6 +1011,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl3rk8.pdf</t>
         </is>
       </c>
@@ -1689,6 +1701,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2031,6 +2048,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2370,6 +2392,11 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl33c8.pdf</t>
         </is>
       </c>
@@ -2715,6 +2742,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3057,6 +3089,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3399,6 +3436,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3741,6 +3783,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4080,6 +4127,11 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl31c8.pdf</t>
         </is>
       </c>
@@ -4425,6 +4477,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4767,6 +4824,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5109,6 +5171,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5448,6 +5515,11 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl30k8.pdf</t>
         </is>
       </c>
@@ -5793,9 +5865,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5818,14 +5895,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5843,6 +5919,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -5855,6 +5932,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -5891,7 +5969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BQ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5962,6 +6040,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6310,6 +6389,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6408,6 +6492,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6745,7 +6830,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7092,6 +7182,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7434,6 +7529,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7771,7 +7871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8118,6 +8223,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8460,6 +8570,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8802,6 +8917,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9144,6 +9264,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9481,7 +9606,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9828,6 +9958,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -10170,6 +10305,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -10512,6 +10652,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -10849,7 +10994,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11196,11 +11346,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
